--- a/outputs/31011.xlsx
+++ b/outputs/31011.xlsx
@@ -121,24 +121,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -334,742 +338,742 @@
   <dimension ref="A1:R20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="10.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="10.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="11.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="10.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="10.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="11.11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="1" t="n">
+      <c r="B1" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="C1" s="2" t="n">
         <v>0.0833333333333333</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="D1" s="2" t="n">
         <v>0.166666666666667</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="E1" s="2" t="n">
         <v>0.25</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="F1" s="2" t="n">
         <v>0.333333333333333</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="G1" s="2" t="n">
         <v>0.416666666666667</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="H1" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="I1" s="2" t="n">
         <v>0.583333333333333</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="J1" s="2" t="n">
         <v>0.666666666666667</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="K1" s="2" t="n">
         <v>0.75</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="L1" s="2" t="n">
         <v>0.833333333333333</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="M1" s="2" t="n">
         <v>0.916666666666667</v>
       </c>
-      <c r="N1" s="1"/>
+      <c r="N1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>45292</v>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>56.6188</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>56.6188</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>56.6188</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>56.6188</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>56.6188</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>56.6188</v>
-      </c>
-      <c r="H2" s="3" t="n">
+      <c r="B2" s="4" t="n">
+        <v>56.6188</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>56.6188</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>56.6188</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>56.6188</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>56.6188</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>56.6188</v>
+      </c>
+      <c r="H2" s="4" t="n">
         <v>45.2944</v>
       </c>
-      <c r="I2" s="3" t="n">
-        <v>56.6188</v>
-      </c>
-      <c r="J2" s="3" t="n">
+      <c r="I2" s="4" t="n">
+        <v>56.6188</v>
+      </c>
+      <c r="J2" s="4" t="n">
         <v>45.2944</v>
       </c>
-      <c r="K2" s="3" t="n">
-        <v>56.6188</v>
-      </c>
-      <c r="L2" s="3" t="n">
+      <c r="K2" s="4" t="n">
+        <v>56.6188</v>
+      </c>
+      <c r="L2" s="4" t="n">
         <v>33.9711</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="M2" s="4" t="n">
         <v>22.6477</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>45293</v>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>56.6188</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>56.6188</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>56.6188</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>56.6188</v>
-      </c>
-      <c r="M3" s="3" t="n">
+      <c r="B3" s="4" t="n">
+        <v>56.6188</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>56.6188</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>56.6188</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>56.6188</v>
+      </c>
+      <c r="M3" s="4" t="n">
         <v>33.9711</v>
       </c>
-      <c r="Q3" s="0" t="s">
+      <c r="Q3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="R3" s="1" t="n">
+      <c r="R3" s="2" t="n">
         <v>0.166666666666667</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>45294</v>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>56.6188</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>56.6188</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="M4" s="3" t="n">
+      <c r="B4" s="4" t="n">
+        <v>56.6188</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>56.6188</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="M4" s="4" t="n">
         <v>45.2944</v>
       </c>
-      <c r="Q4" s="0" t="s">
+      <c r="Q4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="R4" s="1" t="n">
+      <c r="R4" s="2" t="n">
         <v>0.583333333333333</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>45295</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="4" t="n">
         <v>56.4762</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="4" t="n">
         <v>56.4762</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>56.4762</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="4" t="n">
         <v>67.771</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="4" t="n">
         <v>56.4762</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="4" t="n">
         <v>56.4762</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="4" t="n">
         <v>45.1803</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" s="4" t="n">
         <v>56.4762</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J5" s="4" t="n">
         <v>45.1803</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="4" t="n">
         <v>33.8855</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="4" t="n">
         <v>45.1803</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="4" t="n">
         <v>33.8855</v>
       </c>
-      <c r="P5" s="0" t="s">
+      <c r="P5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q5" s="0" t="s">
+      <c r="Q5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>45296</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="4" t="n">
         <v>56.3336</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="4" t="n">
         <v>67.5999</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>67.5999</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>67.5999</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="4" t="n">
         <v>67.5999</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="4" t="n">
         <v>67.5999</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="4" t="n">
         <v>67.5999</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" s="4" t="n">
         <v>67.5999</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J6" s="4" t="n">
         <v>56.3336</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="4" t="n">
         <v>67.5999</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="4" t="n">
         <v>67.5999</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="4" t="n">
         <v>67.5999</v>
       </c>
-      <c r="O6" s="0" t="s">
+      <c r="O6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="P6" s="3" t="n">
         <v>45296</v>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="Q6" s="3" t="n">
         <v>45299</v>
       </c>
-      <c r="R6" s="4" t="n">
-        <f aca="false">SUMPRODUCT((A2:A16&gt;=P6)*(A2:A16&lt;=Q6)*(B1:M1&gt;=R3)*(B1:M1&lt;=R4)*(B2:M16))</f>
+      <c r="R6" s="5" t="n">
+        <f aca="false">SUMPRODUCT((A2:A16&gt;=P6)*(A2:A16&lt;=Q6)*(B1:M1&gt;=R3)*(B1:M1&lt;=R4)*B2:M16)</f>
         <v>1323.8168</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>45297</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="4" t="n">
         <v>45.2944</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="4" t="n">
         <v>33.9711</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>33.9711</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>45.2944</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="4" t="n">
         <v>33.9711</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="4" t="n">
         <v>33.9711</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="4" t="n">
         <v>33.9711</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" s="4" t="n">
         <v>33.9711</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="J7" s="4" t="n">
         <v>33.9711</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="4" t="n">
         <v>33.9711</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="4" t="n">
         <v>45.2944</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="4" t="n">
         <v>33.9711</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>45298</v>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>56.6188</v>
-      </c>
-      <c r="C8" s="3" t="n">
+      <c r="B8" s="4" t="n">
+        <v>56.6188</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>45.2944</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>45.2944</v>
       </c>
-      <c r="E8" s="3" t="n">
-        <v>56.6188</v>
-      </c>
-      <c r="F8" s="3" t="n">
+      <c r="E8" s="4" t="n">
+        <v>56.6188</v>
+      </c>
+      <c r="F8" s="4" t="n">
         <v>45.2944</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="4" t="n">
         <v>45.2944</v>
       </c>
-      <c r="H8" s="3" t="n">
-        <v>56.6188</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>56.6188</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>56.6188</v>
-      </c>
-      <c r="M8" s="3" t="n">
+      <c r="H8" s="4" t="n">
+        <v>56.6188</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>56.6188</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>56.6188</v>
+      </c>
+      <c r="M8" s="4" t="n">
         <v>45.2944</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>45299</v>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>68.1133</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>68.1133</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>68.1133</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>68.1133</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>68.1133</v>
-      </c>
-      <c r="G9" s="3" t="n">
+      <c r="B9" s="4" t="n">
+        <v>68.1133</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>68.1133</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>68.1133</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>68.1133</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>68.1133</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>56.7614</v>
       </c>
-      <c r="H9" s="3" t="n">
-        <v>68.1133</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>68.1133</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>68.1133</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>68.1133</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>68.1133</v>
-      </c>
-      <c r="M9" s="3" t="n">
+      <c r="H9" s="4" t="n">
+        <v>68.1133</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>68.1133</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>68.1133</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>68.1133</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>68.1133</v>
+      </c>
+      <c r="M9" s="4" t="n">
         <v>68.1133</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>45300</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="4" t="n">
         <v>56.7614</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>68.1133</v>
-      </c>
-      <c r="D10" s="3" t="n">
+      <c r="C10" s="4" t="n">
+        <v>68.1133</v>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>56.7614</v>
       </c>
-      <c r="E10" s="3" t="n">
-        <v>68.1133</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>68.1133</v>
-      </c>
-      <c r="G10" s="3" t="n">
+      <c r="E10" s="4" t="n">
+        <v>68.1133</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>68.1133</v>
+      </c>
+      <c r="G10" s="4" t="n">
         <v>56.7614</v>
       </c>
-      <c r="H10" s="3" t="n">
-        <v>68.1133</v>
-      </c>
-      <c r="I10" s="3" t="n">
+      <c r="H10" s="4" t="n">
+        <v>68.1133</v>
+      </c>
+      <c r="I10" s="4" t="n">
         <v>56.7614</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="J10" s="4" t="n">
         <v>56.7614</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" s="4" t="n">
         <v>56.7614</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="4" t="n">
         <v>56.7614</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="4" t="n">
         <v>45.4085</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>45301</v>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>56.6188</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>56.6188</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>67.9421</v>
-      </c>
-      <c r="M11" s="3" t="n">
+      <c r="B11" s="4" t="n">
+        <v>56.6188</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>56.6188</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>67.9421</v>
+      </c>
+      <c r="M11" s="4" t="n">
         <v>67.9421</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>45302</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="4" t="n">
         <v>45.1803</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="4" t="n">
         <v>56.4762</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <v>45.1803</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="4" t="n">
         <v>45.1803</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="4" t="n">
         <v>56.4762</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" s="4" t="n">
         <v>45.1803</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" s="4" t="n">
         <v>45.1803</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" s="4" t="n">
         <v>56.4762</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="J12" s="4" t="n">
         <v>56.4762</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="4" t="n">
         <v>56.4762</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="4" t="n">
         <v>45.1803</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="4" t="n">
         <v>45.1803</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>45303</v>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="4" t="n">
         <v>56.7614</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="4" t="n">
         <v>45.4085</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="4" t="n">
         <v>34.0566</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="4" t="n">
         <v>45.4085</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" s="4" t="n">
         <v>22.7048</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" s="4" t="n">
         <v>34.0566</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" s="4" t="n">
         <v>45.4085</v>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="I13" s="4" t="n">
         <v>34.0566</v>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="J13" s="4" t="n">
         <v>34.0566</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="4" t="n">
         <v>34.0566</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="4" t="n">
         <v>45.4085</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="4" t="n">
         <v>34.0566</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>45304</v>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="4" t="n">
         <v>45.5226</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="4" t="n">
         <v>45.5226</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <v>34.1422</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="4" t="n">
         <v>56.9041</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="4" t="n">
         <v>68.2844</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="4" t="n">
         <v>56.9041</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" s="4" t="n">
         <v>68.2844</v>
       </c>
-      <c r="I14" s="3" t="n">
+      <c r="I14" s="4" t="n">
         <v>68.2844</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="J14" s="4" t="n">
         <v>68.2844</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="4" t="n">
         <v>56.9041</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="4" t="n">
         <v>68.2844</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="4" t="n">
         <v>68.2844</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>45305</v>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="4" t="n">
         <v>34.2278</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="4" t="n">
         <v>34.2278</v>
       </c>
-      <c r="D15" s="3" t="n">
-        <v>45.6367</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>45.6367</v>
-      </c>
-      <c r="F15" s="3" t="n">
+      <c r="D15" s="4" t="n">
+        <v>45.6367</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>45.6367</v>
+      </c>
+      <c r="F15" s="4" t="n">
         <v>57.0467</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" s="4" t="n">
         <v>57.0467</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" s="4" t="n">
         <v>57.0467</v>
       </c>
-      <c r="I15" s="3" t="n">
-        <v>45.6367</v>
-      </c>
-      <c r="J15" s="3" t="n">
+      <c r="I15" s="4" t="n">
+        <v>45.6367</v>
+      </c>
+      <c r="J15" s="4" t="n">
         <v>34.2278</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="4" t="n">
         <v>57.0467</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" s="4" t="n">
         <v>68.4556</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="4" t="n">
         <v>34.2278</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>45306</v>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>45.6367</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>45.6367</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>45.6367</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>45.6367</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>45.6367</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>45.6367</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>45.6367</v>
-      </c>
-      <c r="I16" s="3" t="n">
+      <c r="B16" s="4" t="n">
+        <v>45.6367</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>45.6367</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>45.6367</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>45.6367</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>45.6367</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>45.6367</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>45.6367</v>
+      </c>
+      <c r="I16" s="4" t="n">
         <v>34.2278</v>
       </c>
-      <c r="J16" s="3" t="n">
-        <v>45.6367</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>45.6367</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>45.6367</v>
-      </c>
-      <c r="M16" s="3" t="n">
+      <c r="J16" s="4" t="n">
+        <v>45.6367</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>45.6367</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>45.6367</v>
+      </c>
+      <c r="M16" s="4" t="n">
         <v>34.2278</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M20" s="3"/>
+      <c r="M20" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
